--- a/data_folder/battery/input_data/case.xlsx
+++ b/data_folder/battery/input_data/case.xlsx
@@ -2565,13 +2565,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I26" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H27" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I27" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I29" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I30" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I31" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -2901,13 +2901,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H32" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I32" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I34" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3069,13 +3069,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H35" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I35" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3125,13 +3125,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>
@@ -3181,13 +3181,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="H37" t="n">
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="I37" t="n">
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="H38" t="n">
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="I38" t="n">
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>
@@ -3349,13 +3349,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="H40" t="n">
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="I40" t="n">
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="H41" t="n">
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="I41" t="n">
-        <v/>
+        <v>0.65</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H42" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I42" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="H43" t="n">
-        <v/>
+        <v>0.35</v>
       </c>
       <c r="I43" t="n">
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>from bev_electronics_wiring / _boards: the same shredder, same rates. Copper on the wiring band -- a pack cable is thick and clean.</t>
         </is>
       </c>
     </row>
@@ -3573,13 +3573,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
         </is>
       </c>
     </row>

--- a/data_folder/battery/input_data/case.xlsx
+++ b/data_folder/battery/input_data/case.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1091,12 +1091,76 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F_graphite</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F_p</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+    <dataValidation sqref="E2:E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
       <formula1>=_lists!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
+    <dataValidation sqref="F2:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Unknown value" error="Not one of the values this case declares." type="list">
       <formula1>=_lists!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -1110,7 +1174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4189,13 +4253,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4209,7 +4273,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -4245,13 +4309,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4265,7 +4329,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4477,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4433,7 +4497,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -4469,13 +4533,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4489,7 +4553,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -4525,13 +4589,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4545,7 +4609,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -4693,13 +4757,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4713,7 +4777,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -4861,13 +4925,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v/>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4881,7 +4945,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>
@@ -5554,6 +5618,486 @@
       <c r="L79" t="inlineStr">
         <is>
           <t>assumed: 95/98/100% dismantled, the rest cannot be separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>F_graphite</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v/>
+      </c>
+      <c r="H80" t="n">
+        <v/>
+      </c>
+      <c r="I80" t="n">
+        <v/>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v/>
+      </c>
+      <c r="H81" t="n">
+        <v/>
+      </c>
+      <c r="I81" t="n">
+        <v/>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>F_al_cell</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v/>
+      </c>
+      <c r="H82" t="n">
+        <v/>
+      </c>
+      <c r="I82" t="n">
+        <v/>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v/>
+      </c>
+      <c r="H83" t="n">
+        <v/>
+      </c>
+      <c r="I83" t="n">
+        <v/>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>F_p</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v/>
+      </c>
+      <c r="H84" t="n">
+        <v/>
+      </c>
+      <c r="I84" t="n">
+        <v/>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v/>
+      </c>
+      <c r="H85" t="n">
+        <v/>
+      </c>
+      <c r="I85" t="n">
+        <v/>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: not recovered on this road, so all of it is lost. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: not recovered on this road, so all of it is lost. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: not recovered on this road, so all of it is lost. One destination, therefore 1.0.</t>
         </is>
       </c>
     </row>

--- a/data_folder/battery/input_data/case.xlsx
+++ b/data_folder/battery/input_data/case.xlsx
@@ -11,6 +11,7 @@
     <sheet name="processes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="TCs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="_lists" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="TCs_improved" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3692,15 +3693,6 @@
           <t>Li</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v/>
-      </c>
-      <c r="H45" t="n">
-        <v/>
-      </c>
-      <c r="I45" t="n">
-        <v/>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -3748,15 +3740,6 @@
           <t>Li</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v/>
-      </c>
-      <c r="H46" t="n">
-        <v/>
-      </c>
-      <c r="I46" t="n">
-        <v/>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -3804,15 +3787,6 @@
           <t>Ni</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v/>
-      </c>
-      <c r="H47" t="n">
-        <v/>
-      </c>
-      <c r="I47" t="n">
-        <v/>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -3860,15 +3834,6 @@
           <t>Ni</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v/>
-      </c>
-      <c r="H48" t="n">
-        <v/>
-      </c>
-      <c r="I48" t="n">
-        <v/>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -3916,15 +3881,6 @@
           <t>Co</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v/>
-      </c>
-      <c r="H49" t="n">
-        <v/>
-      </c>
-      <c r="I49" t="n">
-        <v/>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -3972,15 +3928,6 @@
           <t>Co</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v/>
-      </c>
-      <c r="H50" t="n">
-        <v/>
-      </c>
-      <c r="I50" t="n">
-        <v/>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4028,15 +3975,6 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v/>
-      </c>
-      <c r="H51" t="n">
-        <v/>
-      </c>
-      <c r="I51" t="n">
-        <v/>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4084,15 +4022,6 @@
           <t>Mn</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v/>
-      </c>
-      <c r="H52" t="n">
-        <v/>
-      </c>
-      <c r="I52" t="n">
-        <v/>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4140,15 +4069,6 @@
           <t>Fe</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v/>
-      </c>
-      <c r="H53" t="n">
-        <v/>
-      </c>
-      <c r="I53" t="n">
-        <v/>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4196,15 +4116,6 @@
           <t>Fe</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v/>
-      </c>
-      <c r="H54" t="n">
-        <v/>
-      </c>
-      <c r="I54" t="n">
-        <v/>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4364,15 +4275,6 @@
           <t>Li</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v/>
-      </c>
-      <c r="H57" t="n">
-        <v/>
-      </c>
-      <c r="I57" t="n">
-        <v/>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4420,15 +4322,6 @@
           <t>Li</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v/>
-      </c>
-      <c r="H58" t="n">
-        <v/>
-      </c>
-      <c r="I58" t="n">
-        <v/>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4644,15 +4537,6 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v/>
-      </c>
-      <c r="H62" t="n">
-        <v/>
-      </c>
-      <c r="I62" t="n">
-        <v/>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4700,15 +4584,6 @@
           <t>Cu</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v/>
-      </c>
-      <c r="I63" t="n">
-        <v/>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4812,15 +4687,6 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v/>
-      </c>
-      <c r="I65" t="n">
-        <v/>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -4868,15 +4734,6 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v/>
-      </c>
-      <c r="H66" t="n">
-        <v/>
-      </c>
-      <c r="I66" t="n">
-        <v/>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5652,15 +5509,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v/>
-      </c>
-      <c r="H80" t="n">
-        <v/>
-      </c>
-      <c r="I80" t="n">
-        <v/>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5671,7 +5519,6 @@
           <t>hydrometallurgical</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5704,15 +5551,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v/>
-      </c>
-      <c r="H81" t="n">
-        <v/>
-      </c>
-      <c r="I81" t="n">
-        <v/>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5723,7 +5561,6 @@
           <t>hydrometallurgical</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5756,15 +5593,6 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v/>
-      </c>
-      <c r="H82" t="n">
-        <v/>
-      </c>
-      <c r="I82" t="n">
-        <v/>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5775,7 +5603,6 @@
           <t>hydrometallurgical</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5808,15 +5635,6 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v/>
-      </c>
-      <c r="H83" t="n">
-        <v/>
-      </c>
-      <c r="I83" t="n">
-        <v/>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5827,7 +5645,6 @@
           <t>hydrometallurgical</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5860,15 +5677,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v/>
-      </c>
-      <c r="H84" t="n">
-        <v/>
-      </c>
-      <c r="I84" t="n">
-        <v/>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5879,7 +5687,6 @@
           <t>hydrometallurgical</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5912,15 +5719,6 @@
           <t>P</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v/>
-      </c>
-      <c r="H85" t="n">
-        <v/>
-      </c>
-      <c r="I85" t="n">
-        <v/>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>cell_recycling</t>
@@ -5931,7 +5729,6 @@
           <t>hydrometallurgical</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6173,4 +5970,4942 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Input_FlowID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input_layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input_layer_key</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Output_FlowID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TC_target_layer</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TC_target_key</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>value_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>value_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>batteryPackSupportFrame</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>batteryPackSupportFrame</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>batteryPackThermalConductor</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>batteryPackThermalConductor</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>batteryPackCables</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>batteryPackCables</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>batteryCellElectrolyte</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>batteryCellElectrolyte</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>batteryCellSeparator</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>batteryCellSeparator</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>batteryCellCasing</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>batteryCellCasing</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>currentCollectorCathode</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>currentCollectorCathode</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>batteryPackSupportFrame</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>F_fealloy_general</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>batteryPackSupportFrame</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>batteryPackSupportFrame</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>F_alalloy_general</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>F_fealloy_general</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>batteryPackThermalConductor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>F_alalloy_general</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>batteryPackThermalConductor</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>batteryPackThermalConductor</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>batteryPackCables</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>batteryPackCables</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>batteryPackCables</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>F_cu_general</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>F_alalloy_general</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F_pack_housing</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>F_loss_general</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>general_recycling</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>shredder</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Unspecified material -- plastics and the like. Not recovered, which is what makes every recovery figure here a lower bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>F_li</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v/>
+      </c>
+      <c r="H45" t="n">
+        <v/>
+      </c>
+      <c r="I45" t="n">
+        <v/>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v/>
+      </c>
+      <c r="H46" t="n">
+        <v/>
+      </c>
+      <c r="I46" t="n">
+        <v/>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>F_ni</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v/>
+      </c>
+      <c r="H47" t="n">
+        <v/>
+      </c>
+      <c r="I47" t="n">
+        <v/>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ni</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v/>
+      </c>
+      <c r="H48" t="n">
+        <v/>
+      </c>
+      <c r="I48" t="n">
+        <v/>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>F_co</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v/>
+      </c>
+      <c r="H49" t="n">
+        <v/>
+      </c>
+      <c r="I49" t="n">
+        <v/>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v/>
+      </c>
+      <c r="H50" t="n">
+        <v/>
+      </c>
+      <c r="I50" t="n">
+        <v/>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>F_mn</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v/>
+      </c>
+      <c r="H51" t="n">
+        <v/>
+      </c>
+      <c r="I51" t="n">
+        <v/>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v/>
+      </c>
+      <c r="H52" t="n">
+        <v/>
+      </c>
+      <c r="I52" t="n">
+        <v/>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>F_fe_cell</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v/>
+      </c>
+      <c r="H53" t="n">
+        <v/>
+      </c>
+      <c r="I53" t="n">
+        <v/>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v/>
+      </c>
+      <c r="H54" t="n">
+        <v/>
+      </c>
+      <c r="I54" t="n">
+        <v/>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>batteryCellElectrolyte</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>F_li</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v/>
+      </c>
+      <c r="H57" t="n">
+        <v/>
+      </c>
+      <c r="I57" t="n">
+        <v/>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>batteryCellElectrolyte</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v/>
+      </c>
+      <c r="I58" t="n">
+        <v/>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>batteryCellElectrolyte</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>batteryCellSeparator</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>batteryCellCasing</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>F_cu_cell</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v/>
+      </c>
+      <c r="H62" t="n">
+        <v/>
+      </c>
+      <c r="I62" t="n">
+        <v/>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Cu</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v/>
+      </c>
+      <c r="I63" t="n">
+        <v/>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>currentCollectorCathode</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>F_al_cell</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v/>
+      </c>
+      <c r="I65" t="n">
+        <v/>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>currentCollectorCathode</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v/>
+      </c>
+      <c r="H66" t="n">
+        <v/>
+      </c>
+      <c r="I66" t="n">
+        <v/>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>EMPTY -- to be provided. No value is written: this is not a placeholder number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>currentCollectorCathode</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>rest</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Unspecified material -- not recovered, which is what makes every recovery figure here a lower bound. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>batteryPackSupportFrame</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>batteryPackModuleEnclosuresAndCoolantManifolds</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>batteryPackThermalConductor</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>batteryPackCables</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>batteryPackCellTerminals</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>batteryCellElectrolyte</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>batteryCellSeparator</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>batteryCellCasing</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>F_collected</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BEV</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>F_loss_dismantling</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>currentCollectorCathode</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>dismantling</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>UNCHANGED from TCs: no 2060 dismantling rate chosen yet. Every other case improves its disassembly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>F_graphite</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v/>
+      </c>
+      <c r="H80" t="n">
+        <v/>
+      </c>
+      <c r="I80" t="n">
+        <v/>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v/>
+      </c>
+      <c r="H81" t="n">
+        <v/>
+      </c>
+      <c r="I81" t="n">
+        <v/>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>F_al_cell</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v/>
+      </c>
+      <c r="H82" t="n">
+        <v/>
+      </c>
+      <c r="I82" t="n">
+        <v/>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>currentCollectorAnode</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v/>
+      </c>
+      <c r="H83" t="n">
+        <v/>
+      </c>
+      <c r="I83" t="n">
+        <v/>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>F_p</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v/>
+      </c>
+      <c r="H84" t="n">
+        <v/>
+      </c>
+      <c r="I84" t="n">
+        <v/>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v/>
+      </c>
+      <c r="H85" t="n">
+        <v/>
+      </c>
+      <c r="I85" t="n">
+        <v/>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>anodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: not recovered on this road, so all of it is lost. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: not recovered on this road, so all of it is lost. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>F_cells</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>cathodeActiveMaterial</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>F_loss_cell</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>cell_recycling</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>hydrometallurgical</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>DEFINITIONAL: not recovered on this road, so all of it is lost. One destination, therefore 1.0.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data_folder/battery/input_data/case.xlsx
+++ b/data_folder/battery/input_data/case.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rm/Documents/GitHub/RAWCLICRecoveryModel/data_folder/battery/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957AB7CE-48DF-1C4E-9328-709A4F88E627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638C632D-4AE0-1741-AA25-26A2A4C434E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="52340" windowHeight="41680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="1" r:id="rId1"/>
     <sheet name="processes" sheetId="2" r:id="rId2"/>
-    <sheet name="TCs" sheetId="3" r:id="rId3"/>
-    <sheet name="_lists" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="TCs_improved" sheetId="5" r:id="rId5"/>
+    <sheet name="_lists" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="TCs" sheetId="5" r:id="rId4"/>
+    <sheet name="TCs_improved" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="96">
   <si>
     <t>key</t>
   </si>
@@ -303,6 +303,15 @@
   </si>
   <si>
     <t>from bev_electronics_wiring / _boards TCs_improved: the same shredder in 2060.</t>
+  </si>
+  <si>
+    <t>the user's own research, entered 2026-09-17. The 2030 hydrometallurgy rate; no other case in this project uses hydrometallurgy.</t>
+  </si>
+  <si>
+    <t>the user's own research, entered 2026-09-17. The 2060 hydrometallurgy rate; no other case in this project uses hydrometallurgy.</t>
+  </si>
+  <si>
+    <t>the user, 2026-09-17: unchanged from TCs and that is the decision, not an omission -- dismantling is never 100%, so 95/98/100 holds in 2060 too.</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1153,3411 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:L88"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="12" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2">
+        <v>0.98</v>
+      </c>
+      <c r="H2">
+        <v>0.95</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4">
+        <v>0.98</v>
+      </c>
+      <c r="H4">
+        <v>0.95</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>0.98</v>
+      </c>
+      <c r="H6">
+        <v>0.95</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8">
+        <v>0.98</v>
+      </c>
+      <c r="H8">
+        <v>0.95</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>0.98</v>
+      </c>
+      <c r="H10">
+        <v>0.95</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>0.98</v>
+      </c>
+      <c r="H13">
+        <v>0.95</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>0.98</v>
+      </c>
+      <c r="H15">
+        <v>0.95</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17">
+        <v>0.98</v>
+      </c>
+      <c r="H17">
+        <v>0.95</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19">
+        <v>0.98</v>
+      </c>
+      <c r="H19">
+        <v>0.95</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21">
+        <v>0.98</v>
+      </c>
+      <c r="H21">
+        <v>0.95</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23">
+        <v>0.98</v>
+      </c>
+      <c r="H23">
+        <v>0.95</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25">
+        <v>0.98</v>
+      </c>
+      <c r="H25">
+        <v>0.95</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26">
+        <v>0.5</v>
+      </c>
+      <c r="H26">
+        <v>0.35</v>
+      </c>
+      <c r="I26">
+        <v>0.7</v>
+      </c>
+      <c r="J26" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27">
+        <v>0.5</v>
+      </c>
+      <c r="H27">
+        <v>0.35</v>
+      </c>
+      <c r="I27">
+        <v>0.7</v>
+      </c>
+      <c r="J27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29">
+        <v>0.5</v>
+      </c>
+      <c r="H29">
+        <v>0.35</v>
+      </c>
+      <c r="I29">
+        <v>0.7</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30">
+        <v>0.5</v>
+      </c>
+      <c r="H30">
+        <v>0.35</v>
+      </c>
+      <c r="I30">
+        <v>0.7</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31">
+        <v>0.5</v>
+      </c>
+      <c r="H31">
+        <v>0.35</v>
+      </c>
+      <c r="I31">
+        <v>0.7</v>
+      </c>
+      <c r="J31" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32">
+        <v>0.5</v>
+      </c>
+      <c r="H32">
+        <v>0.35</v>
+      </c>
+      <c r="I32">
+        <v>0.7</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34">
+        <v>0.5</v>
+      </c>
+      <c r="H34">
+        <v>0.35</v>
+      </c>
+      <c r="I34">
+        <v>0.7</v>
+      </c>
+      <c r="J34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35">
+        <v>0.5</v>
+      </c>
+      <c r="H35">
+        <v>0.35</v>
+      </c>
+      <c r="I35">
+        <v>0.7</v>
+      </c>
+      <c r="J35" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+      <c r="K36" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37">
+        <v>0.6</v>
+      </c>
+      <c r="H37">
+        <v>0.2</v>
+      </c>
+      <c r="I37">
+        <v>0.9</v>
+      </c>
+      <c r="J37" t="s">
+        <v>32</v>
+      </c>
+      <c r="K37" t="s">
+        <v>33</v>
+      </c>
+      <c r="L37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38">
+        <v>0.4</v>
+      </c>
+      <c r="H38">
+        <v>0.2</v>
+      </c>
+      <c r="I38">
+        <v>0.65</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" t="s">
+        <v>33</v>
+      </c>
+      <c r="L39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40">
+        <v>0.6</v>
+      </c>
+      <c r="H40">
+        <v>0.2</v>
+      </c>
+      <c r="I40">
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" t="s">
+        <v>33</v>
+      </c>
+      <c r="L40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41">
+        <v>0.4</v>
+      </c>
+      <c r="H41">
+        <v>0.2</v>
+      </c>
+      <c r="I41">
+        <v>0.65</v>
+      </c>
+      <c r="J41" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" t="s">
+        <v>33</v>
+      </c>
+      <c r="L41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42">
+        <v>0.5</v>
+      </c>
+      <c r="H42">
+        <v>0.35</v>
+      </c>
+      <c r="I42">
+        <v>0.7</v>
+      </c>
+      <c r="J42" t="s">
+        <v>32</v>
+      </c>
+      <c r="K42" t="s">
+        <v>33</v>
+      </c>
+      <c r="L42" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43">
+        <v>0.5</v>
+      </c>
+      <c r="H43">
+        <v>0.35</v>
+      </c>
+      <c r="I43">
+        <v>0.7</v>
+      </c>
+      <c r="J43" t="s">
+        <v>32</v>
+      </c>
+      <c r="K43" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s">
+        <v>74</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" t="s">
+        <v>33</v>
+      </c>
+      <c r="L44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s">
+        <v>78</v>
+      </c>
+      <c r="G45">
+        <v>0.85</v>
+      </c>
+      <c r="H45">
+        <v>0.7</v>
+      </c>
+      <c r="I45">
+        <v>0.97</v>
+      </c>
+      <c r="J45" t="s">
+        <v>40</v>
+      </c>
+      <c r="K45" t="s">
+        <v>41</v>
+      </c>
+      <c r="L45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>65</v>
+      </c>
+      <c r="D46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46">
+        <v>0.15</v>
+      </c>
+      <c r="H46">
+        <v>0.05</v>
+      </c>
+      <c r="I46">
+        <v>0.2</v>
+      </c>
+      <c r="J46" t="s">
+        <v>40</v>
+      </c>
+      <c r="K46" t="s">
+        <v>41</v>
+      </c>
+      <c r="L46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47">
+        <v>0.95</v>
+      </c>
+      <c r="H47">
+        <v>0.9</v>
+      </c>
+      <c r="I47">
+        <v>0.99</v>
+      </c>
+      <c r="J47" t="s">
+        <v>40</v>
+      </c>
+      <c r="K47" t="s">
+        <v>41</v>
+      </c>
+      <c r="L47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>79</v>
+      </c>
+      <c r="G48">
+        <v>0.05</v>
+      </c>
+      <c r="H48">
+        <v>0.01</v>
+      </c>
+      <c r="I48">
+        <v>0.1</v>
+      </c>
+      <c r="J48" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48" t="s">
+        <v>41</v>
+      </c>
+      <c r="L48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G49">
+        <v>0.95</v>
+      </c>
+      <c r="H49">
+        <v>0.9</v>
+      </c>
+      <c r="I49">
+        <v>0.99</v>
+      </c>
+      <c r="J49" t="s">
+        <v>40</v>
+      </c>
+      <c r="K49" t="s">
+        <v>41</v>
+      </c>
+      <c r="L49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>80</v>
+      </c>
+      <c r="G50">
+        <v>0.05</v>
+      </c>
+      <c r="H50">
+        <v>0.01</v>
+      </c>
+      <c r="I50">
+        <v>0.1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" t="s">
+        <v>41</v>
+      </c>
+      <c r="L50" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s">
+        <v>81</v>
+      </c>
+      <c r="G51">
+        <v>0.9</v>
+      </c>
+      <c r="H51">
+        <v>0.75</v>
+      </c>
+      <c r="I51">
+        <v>0.99</v>
+      </c>
+      <c r="J51" t="s">
+        <v>40</v>
+      </c>
+      <c r="K51" t="s">
+        <v>41</v>
+      </c>
+      <c r="L51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E52" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52">
+        <v>0.1</v>
+      </c>
+      <c r="H52">
+        <v>0.05</v>
+      </c>
+      <c r="I52">
+        <v>0.25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>40</v>
+      </c>
+      <c r="K52" t="s">
+        <v>41</v>
+      </c>
+      <c r="L52" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53">
+        <v>0.8</v>
+      </c>
+      <c r="H53">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I53">
+        <v>0.96</v>
+      </c>
+      <c r="J53" t="s">
+        <v>40</v>
+      </c>
+      <c r="K53" t="s">
+        <v>41</v>
+      </c>
+      <c r="L53" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s">
+        <v>72</v>
+      </c>
+      <c r="G54">
+        <v>0.2</v>
+      </c>
+      <c r="H54">
+        <v>0.05</v>
+      </c>
+      <c r="I54">
+        <v>0.35</v>
+      </c>
+      <c r="J54" t="s">
+        <v>40</v>
+      </c>
+      <c r="K54" t="s">
+        <v>41</v>
+      </c>
+      <c r="L54" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E55" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s">
+        <v>74</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55" t="s">
+        <v>40</v>
+      </c>
+      <c r="K55" t="s">
+        <v>41</v>
+      </c>
+      <c r="L55" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56" t="s">
+        <v>40</v>
+      </c>
+      <c r="K56" t="s">
+        <v>41</v>
+      </c>
+      <c r="L56" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" t="s">
+        <v>44</v>
+      </c>
+      <c r="E57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" t="s">
+        <v>78</v>
+      </c>
+      <c r="G57">
+        <v>0.85</v>
+      </c>
+      <c r="H57">
+        <v>0.7</v>
+      </c>
+      <c r="I57">
+        <v>0.97</v>
+      </c>
+      <c r="J57" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" t="s">
+        <v>41</v>
+      </c>
+      <c r="L57" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" t="s">
+        <v>78</v>
+      </c>
+      <c r="G58">
+        <v>0.15</v>
+      </c>
+      <c r="H58">
+        <v>0.05</v>
+      </c>
+      <c r="I58">
+        <v>0.2</v>
+      </c>
+      <c r="J58" t="s">
+        <v>40</v>
+      </c>
+      <c r="K58" t="s">
+        <v>41</v>
+      </c>
+      <c r="L58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" t="s">
+        <v>48</v>
+      </c>
+      <c r="E59" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
+        <v>40</v>
+      </c>
+      <c r="K59" t="s">
+        <v>41</v>
+      </c>
+      <c r="L59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" t="s">
+        <v>74</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>40</v>
+      </c>
+      <c r="K60" t="s">
+        <v>41</v>
+      </c>
+      <c r="L60" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
+        <v>40</v>
+      </c>
+      <c r="K61" t="s">
+        <v>41</v>
+      </c>
+      <c r="L61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" t="s">
+        <v>39</v>
+      </c>
+      <c r="E62" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G62">
+        <v>0.85</v>
+      </c>
+      <c r="H62">
+        <v>0.66</v>
+      </c>
+      <c r="I62">
+        <v>0.94</v>
+      </c>
+      <c r="J62" t="s">
+        <v>40</v>
+      </c>
+      <c r="K62" t="s">
+        <v>41</v>
+      </c>
+      <c r="L62" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" t="s">
+        <v>77</v>
+      </c>
+      <c r="G63">
+        <v>0.15</v>
+      </c>
+      <c r="H63">
+        <v>0.05</v>
+      </c>
+      <c r="I63">
+        <v>0.4</v>
+      </c>
+      <c r="J63" t="s">
+        <v>40</v>
+      </c>
+      <c r="K63" t="s">
+        <v>41</v>
+      </c>
+      <c r="L63" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" t="s">
+        <v>74</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K64" t="s">
+        <v>41</v>
+      </c>
+      <c r="L64" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" t="s">
+        <v>76</v>
+      </c>
+      <c r="G65">
+        <v>0.72</v>
+      </c>
+      <c r="H65">
+        <v>0.34</v>
+      </c>
+      <c r="I65">
+        <v>0.94</v>
+      </c>
+      <c r="J65" t="s">
+        <v>40</v>
+      </c>
+      <c r="K65" t="s">
+        <v>41</v>
+      </c>
+      <c r="L65" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" t="s">
+        <v>48</v>
+      </c>
+      <c r="E66" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" t="s">
+        <v>76</v>
+      </c>
+      <c r="G66">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H66">
+        <v>0.1</v>
+      </c>
+      <c r="I66">
+        <v>0.5</v>
+      </c>
+      <c r="J66" t="s">
+        <v>40</v>
+      </c>
+      <c r="K66" t="s">
+        <v>41</v>
+      </c>
+      <c r="L66" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+      <c r="D67" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" t="s">
+        <v>74</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67" t="s">
+        <v>40</v>
+      </c>
+      <c r="K67" t="s">
+        <v>41</v>
+      </c>
+      <c r="L67" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E68" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" t="s">
+        <v>59</v>
+      </c>
+      <c r="G68">
+        <v>0.02</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0.05</v>
+      </c>
+      <c r="J68" t="s">
+        <v>26</v>
+      </c>
+      <c r="K68" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" t="s">
+        <v>61</v>
+      </c>
+      <c r="G69">
+        <v>0.02</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0.05</v>
+      </c>
+      <c r="J69" t="s">
+        <v>26</v>
+      </c>
+      <c r="K69" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>49</v>
+      </c>
+      <c r="E70" t="s">
+        <v>28</v>
+      </c>
+      <c r="F70" t="s">
+        <v>62</v>
+      </c>
+      <c r="G70">
+        <v>0.02</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0.05</v>
+      </c>
+      <c r="J70" t="s">
+        <v>26</v>
+      </c>
+      <c r="K70" t="s">
+        <v>27</v>
+      </c>
+      <c r="L70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>49</v>
+      </c>
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" t="s">
+        <v>63</v>
+      </c>
+      <c r="G71">
+        <v>0.02</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0.05</v>
+      </c>
+      <c r="J71" t="s">
+        <v>26</v>
+      </c>
+      <c r="K71" t="s">
+        <v>27</v>
+      </c>
+      <c r="L71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" t="s">
+        <v>64</v>
+      </c>
+      <c r="G72">
+        <v>0.02</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0.05</v>
+      </c>
+      <c r="J72" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>49</v>
+      </c>
+      <c r="E73" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" t="s">
+        <v>65</v>
+      </c>
+      <c r="G73">
+        <v>0.02</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0.05</v>
+      </c>
+      <c r="J73" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73" t="s">
+        <v>27</v>
+      </c>
+      <c r="L73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>49</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" t="s">
+        <v>66</v>
+      </c>
+      <c r="G74">
+        <v>0.02</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0.05</v>
+      </c>
+      <c r="J74" t="s">
+        <v>26</v>
+      </c>
+      <c r="K74" t="s">
+        <v>27</v>
+      </c>
+      <c r="L74" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>49</v>
+      </c>
+      <c r="E75" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" t="s">
+        <v>67</v>
+      </c>
+      <c r="G75">
+        <v>0.02</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0.05</v>
+      </c>
+      <c r="J75" t="s">
+        <v>26</v>
+      </c>
+      <c r="K75" t="s">
+        <v>27</v>
+      </c>
+      <c r="L75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>49</v>
+      </c>
+      <c r="E76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" t="s">
+        <v>68</v>
+      </c>
+      <c r="G76">
+        <v>0.02</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0.05</v>
+      </c>
+      <c r="J76" t="s">
+        <v>26</v>
+      </c>
+      <c r="K76" t="s">
+        <v>27</v>
+      </c>
+      <c r="L76" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>49</v>
+      </c>
+      <c r="E77" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" t="s">
+        <v>69</v>
+      </c>
+      <c r="G77">
+        <v>0.02</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0.05</v>
+      </c>
+      <c r="J77" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" t="s">
+        <v>27</v>
+      </c>
+      <c r="L77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" t="s">
+        <v>49</v>
+      </c>
+      <c r="E78" t="s">
+        <v>28</v>
+      </c>
+      <c r="F78" t="s">
+        <v>70</v>
+      </c>
+      <c r="G78">
+        <v>0.02</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0.05</v>
+      </c>
+      <c r="J78" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" t="s">
+        <v>27</v>
+      </c>
+      <c r="L78" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79">
+        <v>0.02</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0.05</v>
+      </c>
+      <c r="J79" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" t="s">
+        <v>27</v>
+      </c>
+      <c r="L79" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" t="s">
+        <v>66</v>
+      </c>
+      <c r="D80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E80" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80">
+        <v>0.5</v>
+      </c>
+      <c r="H80">
+        <v>0.3</v>
+      </c>
+      <c r="I80">
+        <v>0.7</v>
+      </c>
+      <c r="J80" t="s">
+        <v>40</v>
+      </c>
+      <c r="K80" t="s">
+        <v>41</v>
+      </c>
+      <c r="L80" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" t="s">
+        <v>66</v>
+      </c>
+      <c r="D81" t="s">
+        <v>48</v>
+      </c>
+      <c r="E81" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81">
+        <v>0.5</v>
+      </c>
+      <c r="H81">
+        <v>0.3</v>
+      </c>
+      <c r="I81">
+        <v>0.7</v>
+      </c>
+      <c r="J81" t="s">
+        <v>40</v>
+      </c>
+      <c r="K81" t="s">
+        <v>41</v>
+      </c>
+      <c r="L81" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" t="s">
+        <v>42</v>
+      </c>
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" t="s">
+        <v>76</v>
+      </c>
+      <c r="G82">
+        <v>0.72</v>
+      </c>
+      <c r="H82">
+        <v>0.34</v>
+      </c>
+      <c r="I82">
+        <v>0.94</v>
+      </c>
+      <c r="J82" t="s">
+        <v>40</v>
+      </c>
+      <c r="K82" t="s">
+        <v>41</v>
+      </c>
+      <c r="L82" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" t="s">
+        <v>76</v>
+      </c>
+      <c r="G83">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H83">
+        <v>0.1</v>
+      </c>
+      <c r="I83">
+        <v>0.5</v>
+      </c>
+      <c r="J83" t="s">
+        <v>40</v>
+      </c>
+      <c r="K83" t="s">
+        <v>41</v>
+      </c>
+      <c r="L83" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" t="s">
+        <v>65</v>
+      </c>
+      <c r="D84" t="s">
+        <v>51</v>
+      </c>
+      <c r="E84" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" t="s">
+        <v>85</v>
+      </c>
+      <c r="G84">
+        <v>0.8</v>
+      </c>
+      <c r="H84">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I84">
+        <v>0.97</v>
+      </c>
+      <c r="J84" t="s">
+        <v>40</v>
+      </c>
+      <c r="K84" t="s">
+        <v>41</v>
+      </c>
+      <c r="L84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85">
+        <v>0.2</v>
+      </c>
+      <c r="H85">
+        <v>0.1</v>
+      </c>
+      <c r="I85">
+        <v>0.4</v>
+      </c>
+      <c r="J85" t="s">
+        <v>40</v>
+      </c>
+      <c r="K85" t="s">
+        <v>41</v>
+      </c>
+      <c r="L85" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86" t="s">
+        <v>48</v>
+      </c>
+      <c r="E86" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" t="s">
+        <v>86</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86" t="s">
+        <v>40</v>
+      </c>
+      <c r="K86" t="s">
+        <v>41</v>
+      </c>
+      <c r="L86" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87" t="s">
+        <v>48</v>
+      </c>
+      <c r="E87" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" t="s">
+        <v>88</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87" t="s">
+        <v>40</v>
+      </c>
+      <c r="K87" t="s">
+        <v>41</v>
+      </c>
+      <c r="L87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88" t="s">
+        <v>48</v>
+      </c>
+      <c r="E88" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" t="s">
+        <v>76</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
+        <v>40</v>
+      </c>
+      <c r="K88" t="s">
+        <v>41</v>
+      </c>
+      <c r="L88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872A0DA9-C130-8B44-B285-5AD7955DC436}">
   <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1226,7 +4639,7 @@
         <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1264,7 +4677,7 @@
         <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1302,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="L4" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1340,7 +4753,7 @@
         <v>27</v>
       </c>
       <c r="L5" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1378,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1416,7 +4829,7 @@
         <v>27</v>
       </c>
       <c r="L7" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1454,7 +4867,7 @@
         <v>27</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1492,7 +4905,7 @@
         <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1530,7 +4943,7 @@
         <v>27</v>
       </c>
       <c r="L10" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1568,7 +4981,7 @@
         <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1606,7 +5019,7 @@
         <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1644,7 +5057,7 @@
         <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1682,7 +5095,7 @@
         <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1720,7 +5133,7 @@
         <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1758,7 +5171,7 @@
         <v>27</v>
       </c>
       <c r="L16" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1796,7 +5209,7 @@
         <v>27</v>
       </c>
       <c r="L17" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -1834,7 +5247,7 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -1872,7 +5285,7 @@
         <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -1910,7 +5323,7 @@
         <v>27</v>
       </c>
       <c r="L20" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -1948,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -1986,7 +5399,7 @@
         <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -2024,7 +5437,7 @@
         <v>27</v>
       </c>
       <c r="L23" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -2062,7 +5475,7 @@
         <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -2100,7 +5513,7 @@
         <v>27</v>
       </c>
       <c r="L25" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -2123,13 +5536,13 @@
         <v>72</v>
       </c>
       <c r="G26">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H26">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I26">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J26" t="s">
         <v>32</v>
@@ -2138,7 +5551,7 @@
         <v>33</v>
       </c>
       <c r="L26" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -2161,13 +5574,13 @@
         <v>72</v>
       </c>
       <c r="G27">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H27">
+        <v>0.1</v>
+      </c>
+      <c r="I27">
         <v>0.5</v>
-      </c>
-      <c r="H27">
-        <v>0.35</v>
-      </c>
-      <c r="I27">
-        <v>0.7</v>
       </c>
       <c r="J27" t="s">
         <v>32</v>
@@ -2176,7 +5589,7 @@
         <v>33</v>
       </c>
       <c r="L27" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -2237,13 +5650,13 @@
         <v>76</v>
       </c>
       <c r="G29">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H29">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I29">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J29" t="s">
         <v>32</v>
@@ -2252,7 +5665,7 @@
         <v>33</v>
       </c>
       <c r="L29" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -2275,13 +5688,13 @@
         <v>76</v>
       </c>
       <c r="G30">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H30">
+        <v>0.1</v>
+      </c>
+      <c r="I30">
         <v>0.5</v>
-      </c>
-      <c r="H30">
-        <v>0.35</v>
-      </c>
-      <c r="I30">
-        <v>0.7</v>
       </c>
       <c r="J30" t="s">
         <v>32</v>
@@ -2290,7 +5703,7 @@
         <v>33</v>
       </c>
       <c r="L30" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -2313,13 +5726,13 @@
         <v>72</v>
       </c>
       <c r="G31">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H31">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I31">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J31" t="s">
         <v>32</v>
@@ -2328,7 +5741,7 @@
         <v>33</v>
       </c>
       <c r="L31" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -2351,13 +5764,13 @@
         <v>72</v>
       </c>
       <c r="G32">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H32">
+        <v>0.1</v>
+      </c>
+      <c r="I32">
         <v>0.5</v>
-      </c>
-      <c r="H32">
-        <v>0.35</v>
-      </c>
-      <c r="I32">
-        <v>0.7</v>
       </c>
       <c r="J32" t="s">
         <v>32</v>
@@ -2366,7 +5779,7 @@
         <v>33</v>
       </c>
       <c r="L32" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -2427,13 +5840,13 @@
         <v>76</v>
       </c>
       <c r="G34">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H34">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I34">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J34" t="s">
         <v>32</v>
@@ -2442,7 +5855,7 @@
         <v>33</v>
       </c>
       <c r="L34" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -2465,13 +5878,13 @@
         <v>76</v>
       </c>
       <c r="G35">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H35">
+        <v>0.1</v>
+      </c>
+      <c r="I35">
         <v>0.5</v>
-      </c>
-      <c r="H35">
-        <v>0.35</v>
-      </c>
-      <c r="I35">
-        <v>0.7</v>
       </c>
       <c r="J35" t="s">
         <v>32</v>
@@ -2480,7 +5893,7 @@
         <v>33</v>
       </c>
       <c r="L35" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -2541,13 +5954,13 @@
         <v>77</v>
       </c>
       <c r="G37">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="H37">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="I37">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="J37" t="s">
         <v>32</v>
@@ -2556,7 +5969,7 @@
         <v>33</v>
       </c>
       <c r="L37" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -2579,13 +5992,13 @@
         <v>77</v>
       </c>
       <c r="G38">
+        <v>0.15</v>
+      </c>
+      <c r="H38">
+        <v>0.05</v>
+      </c>
+      <c r="I38">
         <v>0.4</v>
-      </c>
-      <c r="H38">
-        <v>0.2</v>
-      </c>
-      <c r="I38">
-        <v>0.65</v>
       </c>
       <c r="J38" t="s">
         <v>32</v>
@@ -2594,7 +6007,7 @@
         <v>33</v>
       </c>
       <c r="L38" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -2655,13 +6068,13 @@
         <v>77</v>
       </c>
       <c r="G40">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="H40">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="I40">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="J40" t="s">
         <v>32</v>
@@ -2670,7 +6083,7 @@
         <v>33</v>
       </c>
       <c r="L40" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -2693,13 +6106,13 @@
         <v>77</v>
       </c>
       <c r="G41">
+        <v>0.15</v>
+      </c>
+      <c r="H41">
+        <v>0.05</v>
+      </c>
+      <c r="I41">
         <v>0.4</v>
-      </c>
-      <c r="H41">
-        <v>0.2</v>
-      </c>
-      <c r="I41">
-        <v>0.65</v>
       </c>
       <c r="J41" t="s">
         <v>32</v>
@@ -2708,7 +6121,7 @@
         <v>33</v>
       </c>
       <c r="L41" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -2731,13 +6144,13 @@
         <v>76</v>
       </c>
       <c r="G42">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H42">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I42">
-        <v>0.7</v>
+        <v>0.94</v>
       </c>
       <c r="J42" t="s">
         <v>32</v>
@@ -2746,7 +6159,7 @@
         <v>33</v>
       </c>
       <c r="L42" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
@@ -2769,13 +6182,13 @@
         <v>76</v>
       </c>
       <c r="G43">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H43">
+        <v>0.1</v>
+      </c>
+      <c r="I43">
         <v>0.5</v>
-      </c>
-      <c r="H43">
-        <v>0.35</v>
-      </c>
-      <c r="I43">
-        <v>0.7</v>
       </c>
       <c r="J43" t="s">
         <v>32</v>
@@ -2784,7 +6197,7 @@
         <v>33</v>
       </c>
       <c r="L43" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -2844,6 +6257,15 @@
       <c r="F45" t="s">
         <v>78</v>
       </c>
+      <c r="G45">
+        <v>0.96</v>
+      </c>
+      <c r="H45">
+        <v>0.85</v>
+      </c>
+      <c r="I45">
+        <v>0.99</v>
+      </c>
       <c r="J45" t="s">
         <v>40</v>
       </c>
@@ -2851,7 +6273,7 @@
         <v>41</v>
       </c>
       <c r="L45" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -2873,6 +6295,15 @@
       <c r="F46" t="s">
         <v>78</v>
       </c>
+      <c r="G46">
+        <v>0.04</v>
+      </c>
+      <c r="H46">
+        <v>0.01</v>
+      </c>
+      <c r="I46">
+        <v>0.15</v>
+      </c>
       <c r="J46" t="s">
         <v>40</v>
       </c>
@@ -2880,7 +6311,7 @@
         <v>41</v>
       </c>
       <c r="L46" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -2902,6 +6333,15 @@
       <c r="F47" t="s">
         <v>79</v>
       </c>
+      <c r="G47">
+        <v>0.99</v>
+      </c>
+      <c r="H47">
+        <v>0.96</v>
+      </c>
+      <c r="I47">
+        <v>0.99</v>
+      </c>
       <c r="J47" t="s">
         <v>40</v>
       </c>
@@ -2909,7 +6349,7 @@
         <v>41</v>
       </c>
       <c r="L47" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -2931,6 +6371,15 @@
       <c r="F48" t="s">
         <v>79</v>
       </c>
+      <c r="G48">
+        <v>0.01</v>
+      </c>
+      <c r="H48">
+        <v>2E-3</v>
+      </c>
+      <c r="I48">
+        <v>0.02</v>
+      </c>
       <c r="J48" t="s">
         <v>40</v>
       </c>
@@ -2938,7 +6387,7 @@
         <v>41</v>
       </c>
       <c r="L48" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -2960,6 +6409,15 @@
       <c r="F49" t="s">
         <v>80</v>
       </c>
+      <c r="G49">
+        <v>0.99</v>
+      </c>
+      <c r="H49">
+        <v>0.96</v>
+      </c>
+      <c r="I49">
+        <v>0.99</v>
+      </c>
       <c r="J49" t="s">
         <v>40</v>
       </c>
@@ -2967,7 +6425,7 @@
         <v>41</v>
       </c>
       <c r="L49" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -2989,6 +6447,15 @@
       <c r="F50" t="s">
         <v>80</v>
       </c>
+      <c r="G50">
+        <v>0.01</v>
+      </c>
+      <c r="H50">
+        <v>2E-3</v>
+      </c>
+      <c r="I50">
+        <v>0.02</v>
+      </c>
       <c r="J50" t="s">
         <v>40</v>
       </c>
@@ -2996,7 +6463,7 @@
         <v>41</v>
       </c>
       <c r="L50" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
@@ -3018,6 +6485,15 @@
       <c r="F51" t="s">
         <v>81</v>
       </c>
+      <c r="G51">
+        <v>0.98</v>
+      </c>
+      <c r="H51">
+        <v>0.92</v>
+      </c>
+      <c r="I51">
+        <v>0.99</v>
+      </c>
       <c r="J51" t="s">
         <v>40</v>
       </c>
@@ -3025,7 +6501,7 @@
         <v>41</v>
       </c>
       <c r="L51" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -3047,6 +6523,15 @@
       <c r="F52" t="s">
         <v>81</v>
       </c>
+      <c r="G52">
+        <v>0.02</v>
+      </c>
+      <c r="H52">
+        <v>0.01</v>
+      </c>
+      <c r="I52">
+        <v>0.1</v>
+      </c>
       <c r="J52" t="s">
         <v>40</v>
       </c>
@@ -3054,7 +6539,7 @@
         <v>41</v>
       </c>
       <c r="L52" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
@@ -3076,6 +6561,15 @@
       <c r="F53" t="s">
         <v>72</v>
       </c>
+      <c r="G53">
+        <v>0.94</v>
+      </c>
+      <c r="H53">
+        <v>0.8</v>
+      </c>
+      <c r="I53">
+        <v>0.99</v>
+      </c>
       <c r="J53" t="s">
         <v>40</v>
       </c>
@@ -3083,7 +6577,7 @@
         <v>41</v>
       </c>
       <c r="L53" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
@@ -3105,6 +6599,15 @@
       <c r="F54" t="s">
         <v>72</v>
       </c>
+      <c r="G54">
+        <v>0.06</v>
+      </c>
+      <c r="H54">
+        <v>0.02</v>
+      </c>
+      <c r="I54">
+        <v>0.15</v>
+      </c>
       <c r="J54" t="s">
         <v>40</v>
       </c>
@@ -3112,7 +6615,7 @@
         <v>41</v>
       </c>
       <c r="L54" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
@@ -3210,6 +6713,15 @@
       <c r="F57" t="s">
         <v>78</v>
       </c>
+      <c r="G57">
+        <v>0.96</v>
+      </c>
+      <c r="H57">
+        <v>0.85</v>
+      </c>
+      <c r="I57">
+        <v>0.99</v>
+      </c>
       <c r="J57" t="s">
         <v>40</v>
       </c>
@@ -3217,7 +6729,7 @@
         <v>41</v>
       </c>
       <c r="L57" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -3239,6 +6751,15 @@
       <c r="F58" t="s">
         <v>78</v>
       </c>
+      <c r="G58">
+        <v>0.04</v>
+      </c>
+      <c r="H58">
+        <v>0.01</v>
+      </c>
+      <c r="I58">
+        <v>0.15</v>
+      </c>
       <c r="J58" t="s">
         <v>40</v>
       </c>
@@ -3246,7 +6767,7 @@
         <v>41</v>
       </c>
       <c r="L58" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -3382,6 +6903,15 @@
       <c r="F62" t="s">
         <v>77</v>
       </c>
+      <c r="G62">
+        <v>0.92</v>
+      </c>
+      <c r="H62">
+        <v>0.85</v>
+      </c>
+      <c r="I62">
+        <v>0.97</v>
+      </c>
       <c r="J62" t="s">
         <v>40</v>
       </c>
@@ -3389,7 +6919,7 @@
         <v>41</v>
       </c>
       <c r="L62" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -3411,6 +6941,15 @@
       <c r="F63" t="s">
         <v>77</v>
       </c>
+      <c r="G63">
+        <v>0.08</v>
+      </c>
+      <c r="H63">
+        <v>0.02</v>
+      </c>
+      <c r="I63">
+        <v>0.2</v>
+      </c>
       <c r="J63" t="s">
         <v>40</v>
       </c>
@@ -3418,7 +6957,7 @@
         <v>41</v>
       </c>
       <c r="L63" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -3478,6 +7017,15 @@
       <c r="F65" t="s">
         <v>76</v>
       </c>
+      <c r="G65">
+        <v>0.85</v>
+      </c>
+      <c r="H65">
+        <v>0.65</v>
+      </c>
+      <c r="I65">
+        <v>0.98</v>
+      </c>
       <c r="J65" t="s">
         <v>40</v>
       </c>
@@ -3485,7 +7033,7 @@
         <v>41</v>
       </c>
       <c r="L65" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -3507,6 +7055,15 @@
       <c r="F66" t="s">
         <v>76</v>
       </c>
+      <c r="G66">
+        <v>0.15</v>
+      </c>
+      <c r="H66">
+        <v>0.05</v>
+      </c>
+      <c r="I66">
+        <v>0.4</v>
+      </c>
       <c r="J66" t="s">
         <v>40</v>
       </c>
@@ -3514,7 +7071,7 @@
         <v>41</v>
       </c>
       <c r="L66" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -3590,7 +7147,7 @@
         <v>27</v>
       </c>
       <c r="L68" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -3628,7 +7185,7 @@
         <v>27</v>
       </c>
       <c r="L69" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -3666,7 +7223,7 @@
         <v>27</v>
       </c>
       <c r="L70" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -3704,7 +7261,7 @@
         <v>27</v>
       </c>
       <c r="L71" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -3742,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="L72" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -3780,7 +7337,7 @@
         <v>27</v>
       </c>
       <c r="L73" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -3818,7 +7375,7 @@
         <v>27</v>
       </c>
       <c r="L74" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -3856,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="L75" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -3894,7 +7451,7 @@
         <v>27</v>
       </c>
       <c r="L76" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -3932,7 +7489,7 @@
         <v>27</v>
       </c>
       <c r="L77" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -3970,7 +7527,7 @@
         <v>27</v>
       </c>
       <c r="L78" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -4008,7 +7565,7 @@
         <v>27</v>
       </c>
       <c r="L79" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -4030,12 +7587,24 @@
       <c r="F80" t="s">
         <v>84</v>
       </c>
+      <c r="G80">
+        <v>0.7</v>
+      </c>
+      <c r="H80">
+        <v>0.6</v>
+      </c>
+      <c r="I80">
+        <v>0.85</v>
+      </c>
       <c r="J80" t="s">
         <v>40</v>
       </c>
       <c r="K80" t="s">
         <v>41</v>
       </c>
+      <c r="L80" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
@@ -4056,12 +7625,24 @@
       <c r="F81" t="s">
         <v>84</v>
       </c>
+      <c r="G81">
+        <v>0.3</v>
+      </c>
+      <c r="H81">
+        <v>0.1</v>
+      </c>
+      <c r="I81">
+        <v>0.5</v>
+      </c>
       <c r="J81" t="s">
         <v>40</v>
       </c>
       <c r="K81" t="s">
         <v>41</v>
       </c>
+      <c r="L81" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
@@ -4082,12 +7663,24 @@
       <c r="F82" t="s">
         <v>76</v>
       </c>
+      <c r="G82">
+        <v>0.85</v>
+      </c>
+      <c r="H82">
+        <v>0.65</v>
+      </c>
+      <c r="I82">
+        <v>0.98</v>
+      </c>
       <c r="J82" t="s">
         <v>40</v>
       </c>
       <c r="K82" t="s">
         <v>41</v>
       </c>
+      <c r="L82" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
@@ -4108,12 +7701,24 @@
       <c r="F83" t="s">
         <v>76</v>
       </c>
+      <c r="G83">
+        <v>0.15</v>
+      </c>
+      <c r="H83">
+        <v>0.05</v>
+      </c>
+      <c r="I83">
+        <v>0.4</v>
+      </c>
       <c r="J83" t="s">
         <v>40</v>
       </c>
       <c r="K83" t="s">
         <v>41</v>
       </c>
+      <c r="L83" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
@@ -4134,12 +7739,24 @@
       <c r="F84" t="s">
         <v>85</v>
       </c>
+      <c r="G84">
+        <v>0.94</v>
+      </c>
+      <c r="H84">
+        <v>0.77</v>
+      </c>
+      <c r="I84">
+        <v>0.99</v>
+      </c>
       <c r="J84" t="s">
         <v>40</v>
       </c>
       <c r="K84" t="s">
         <v>41</v>
       </c>
+      <c r="L84" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
@@ -4160,3325 +7777,23 @@
       <c r="F85" t="s">
         <v>85</v>
       </c>
+      <c r="G85">
+        <v>0.06</v>
+      </c>
+      <c r="H85">
+        <v>0.02</v>
+      </c>
+      <c r="I85">
+        <v>0.25</v>
+      </c>
       <c r="J85" t="s">
         <v>40</v>
       </c>
       <c r="K85" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>30</v>
-      </c>
-      <c r="B86" t="s">
-        <v>28</v>
-      </c>
-      <c r="C86" t="s">
-        <v>66</v>
-      </c>
-      <c r="D86" t="s">
-        <v>48</v>
-      </c>
-      <c r="E86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="s">
-        <v>86</v>
-      </c>
-      <c r="G86">
-        <v>1</v>
-      </c>
-      <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="I86">
-        <v>1</v>
-      </c>
-      <c r="J86" t="s">
-        <v>40</v>
-      </c>
-      <c r="K86" t="s">
-        <v>41</v>
-      </c>
-      <c r="L86" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>30</v>
-      </c>
-      <c r="B87" t="s">
-        <v>28</v>
-      </c>
-      <c r="C87" t="s">
-        <v>65</v>
-      </c>
-      <c r="D87" t="s">
-        <v>48</v>
-      </c>
-      <c r="E87" t="s">
-        <v>11</v>
-      </c>
-      <c r="F87" t="s">
-        <v>88</v>
-      </c>
-      <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <v>1</v>
-      </c>
-      <c r="I87">
-        <v>1</v>
-      </c>
-      <c r="J87" t="s">
-        <v>40</v>
-      </c>
-      <c r="K87" t="s">
-        <v>41</v>
-      </c>
-      <c r="L87" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>30</v>
-      </c>
-      <c r="B88" t="s">
-        <v>28</v>
-      </c>
-      <c r="C88" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" t="s">
-        <v>48</v>
-      </c>
-      <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" t="s">
-        <v>76</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
-      <c r="H88">
-        <v>1</v>
-      </c>
-      <c r="I88">
-        <v>1</v>
-      </c>
-      <c r="J88" t="s">
-        <v>40</v>
-      </c>
-      <c r="K88" t="s">
-        <v>41</v>
-      </c>
-      <c r="L88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L88"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="12" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2">
-        <v>0.98</v>
-      </c>
-      <c r="H2">
-        <v>0.95</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4">
-        <v>0.98</v>
-      </c>
-      <c r="H4">
-        <v>0.95</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>0.98</v>
-      </c>
-      <c r="H6">
-        <v>0.95</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8">
-        <v>0.98</v>
-      </c>
-      <c r="H8">
-        <v>0.95</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>0.98</v>
-      </c>
-      <c r="H10">
-        <v>0.95</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
-        <v>0.98</v>
-      </c>
-      <c r="H13">
-        <v>0.95</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>0.98</v>
-      </c>
-      <c r="H15">
-        <v>0.95</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17">
-        <v>0.98</v>
-      </c>
-      <c r="H17">
-        <v>0.95</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19">
-        <v>0.98</v>
-      </c>
-      <c r="H19">
-        <v>0.95</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>26</v>
-      </c>
-      <c r="K20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21">
-        <v>0.98</v>
-      </c>
-      <c r="H21">
-        <v>0.95</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21" t="s">
-        <v>26</v>
-      </c>
-      <c r="K21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23">
-        <v>0.98</v>
-      </c>
-      <c r="H23">
-        <v>0.95</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-      <c r="J23" t="s">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
-        <v>26</v>
-      </c>
-      <c r="K24" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25">
-        <v>0.98</v>
-      </c>
-      <c r="H25">
-        <v>0.95</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25" t="s">
-        <v>26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26">
-        <v>0.72</v>
-      </c>
-      <c r="H26">
-        <v>0.34</v>
-      </c>
-      <c r="I26">
-        <v>0.94</v>
-      </c>
-      <c r="J26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" t="s">
-        <v>33</v>
-      </c>
-      <c r="L26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H27">
-        <v>0.1</v>
-      </c>
-      <c r="I27">
-        <v>0.5</v>
-      </c>
-      <c r="J27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K27" t="s">
-        <v>33</v>
-      </c>
-      <c r="L27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28" t="s">
-        <v>32</v>
-      </c>
-      <c r="K28" t="s">
-        <v>33</v>
-      </c>
-      <c r="L28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29">
-        <v>0.72</v>
-      </c>
-      <c r="H29">
-        <v>0.34</v>
-      </c>
-      <c r="I29">
-        <v>0.94</v>
-      </c>
-      <c r="J29" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" t="s">
-        <v>33</v>
-      </c>
-      <c r="L29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" t="s">
-        <v>61</v>
-      </c>
-      <c r="D30" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H30">
-        <v>0.1</v>
-      </c>
-      <c r="I30">
-        <v>0.5</v>
-      </c>
-      <c r="J30" t="s">
-        <v>32</v>
-      </c>
-      <c r="K30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" t="s">
-        <v>61</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31">
-        <v>0.72</v>
-      </c>
-      <c r="H31">
-        <v>0.34</v>
-      </c>
-      <c r="I31">
-        <v>0.94</v>
-      </c>
-      <c r="J31" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" t="s">
-        <v>33</v>
-      </c>
-      <c r="L31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H32">
-        <v>0.1</v>
-      </c>
-      <c r="I32">
-        <v>0.5</v>
-      </c>
-      <c r="J32" t="s">
-        <v>32</v>
-      </c>
-      <c r="K32" t="s">
-        <v>33</v>
-      </c>
-      <c r="L32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-      <c r="J33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" t="s">
-        <v>33</v>
-      </c>
-      <c r="L33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34">
-        <v>0.72</v>
-      </c>
-      <c r="H34">
-        <v>0.34</v>
-      </c>
-      <c r="I34">
-        <v>0.94</v>
-      </c>
-      <c r="J34" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" t="s">
-        <v>33</v>
-      </c>
-      <c r="L34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H35">
-        <v>0.1</v>
-      </c>
-      <c r="I35">
-        <v>0.5</v>
-      </c>
-      <c r="J35" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" t="s">
-        <v>33</v>
-      </c>
-      <c r="L35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" t="s">
-        <v>74</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-      <c r="J36" t="s">
-        <v>32</v>
-      </c>
-      <c r="K36" t="s">
-        <v>33</v>
-      </c>
-      <c r="L36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G37">
-        <v>0.85</v>
-      </c>
-      <c r="H37">
-        <v>0.66</v>
-      </c>
-      <c r="I37">
-        <v>0.94</v>
-      </c>
-      <c r="J37" t="s">
-        <v>32</v>
-      </c>
-      <c r="K37" t="s">
-        <v>33</v>
-      </c>
-      <c r="L37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" t="s">
-        <v>63</v>
-      </c>
-      <c r="D38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>77</v>
-      </c>
-      <c r="G38">
-        <v>0.15</v>
-      </c>
-      <c r="H38">
-        <v>0.05</v>
-      </c>
-      <c r="I38">
-        <v>0.4</v>
-      </c>
-      <c r="J38" t="s">
-        <v>32</v>
-      </c>
-      <c r="K38" t="s">
-        <v>33</v>
-      </c>
-      <c r="L38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" t="s">
-        <v>74</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39" t="s">
-        <v>32</v>
-      </c>
-      <c r="K39" t="s">
-        <v>33</v>
-      </c>
-      <c r="L39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40">
-        <v>0.85</v>
-      </c>
-      <c r="H40">
-        <v>0.66</v>
-      </c>
-      <c r="I40">
-        <v>0.94</v>
-      </c>
-      <c r="J40" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" t="s">
-        <v>33</v>
-      </c>
-      <c r="L40" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" t="s">
-        <v>37</v>
-      </c>
-      <c r="E41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" t="s">
-        <v>77</v>
-      </c>
-      <c r="G41">
-        <v>0.15</v>
-      </c>
-      <c r="H41">
-        <v>0.05</v>
-      </c>
-      <c r="I41">
-        <v>0.4</v>
-      </c>
-      <c r="J41" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" t="s">
-        <v>33</v>
-      </c>
-      <c r="L41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>25</v>
-      </c>
-      <c r="B42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42">
-        <v>0.72</v>
-      </c>
-      <c r="H42">
-        <v>0.34</v>
-      </c>
-      <c r="I42">
-        <v>0.94</v>
-      </c>
-      <c r="J42" t="s">
-        <v>32</v>
-      </c>
-      <c r="K42" t="s">
-        <v>33</v>
-      </c>
-      <c r="L42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" t="s">
-        <v>64</v>
-      </c>
-      <c r="D43" t="s">
-        <v>37</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>76</v>
-      </c>
-      <c r="G43">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H43">
-        <v>0.1</v>
-      </c>
-      <c r="I43">
-        <v>0.5</v>
-      </c>
-      <c r="J43" t="s">
-        <v>32</v>
-      </c>
-      <c r="K43" t="s">
-        <v>33</v>
-      </c>
-      <c r="L43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-      <c r="J44" t="s">
-        <v>32</v>
-      </c>
-      <c r="K44" t="s">
-        <v>33</v>
-      </c>
-      <c r="L44" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>78</v>
-      </c>
-      <c r="G45">
-        <v>0.85</v>
-      </c>
-      <c r="H45">
-        <v>0.7</v>
-      </c>
-      <c r="I45">
-        <v>0.97</v>
-      </c>
-      <c r="J45" t="s">
-        <v>40</v>
-      </c>
-      <c r="K45" t="s">
-        <v>41</v>
-      </c>
-      <c r="L45" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" t="s">
-        <v>65</v>
-      </c>
-      <c r="D46" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>78</v>
-      </c>
-      <c r="G46">
-        <v>0.15</v>
-      </c>
-      <c r="H46">
-        <v>0.05</v>
-      </c>
-      <c r="I46">
-        <v>0.2</v>
-      </c>
-      <c r="J46" t="s">
-        <v>40</v>
-      </c>
-      <c r="K46" t="s">
-        <v>41</v>
-      </c>
-      <c r="L46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" t="s">
-        <v>79</v>
-      </c>
-      <c r="G47">
-        <v>0.95</v>
-      </c>
-      <c r="H47">
-        <v>0.9</v>
-      </c>
-      <c r="I47">
-        <v>0.99</v>
-      </c>
-      <c r="J47" t="s">
-        <v>40</v>
-      </c>
-      <c r="K47" t="s">
-        <v>41</v>
-      </c>
-      <c r="L47" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" t="s">
-        <v>79</v>
-      </c>
-      <c r="G48">
-        <v>0.05</v>
-      </c>
-      <c r="H48">
-        <v>0.01</v>
-      </c>
-      <c r="I48">
-        <v>0.1</v>
-      </c>
-      <c r="J48" t="s">
-        <v>40</v>
-      </c>
-      <c r="K48" t="s">
-        <v>41</v>
-      </c>
-      <c r="L48" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" t="s">
-        <v>46</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="s">
-        <v>80</v>
-      </c>
-      <c r="G49">
-        <v>0.95</v>
-      </c>
-      <c r="H49">
-        <v>0.9</v>
-      </c>
-      <c r="I49">
-        <v>0.99</v>
-      </c>
-      <c r="J49" t="s">
-        <v>40</v>
-      </c>
-      <c r="K49" t="s">
-        <v>41</v>
-      </c>
-      <c r="L49" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" t="s">
-        <v>80</v>
-      </c>
-      <c r="G50">
-        <v>0.05</v>
-      </c>
-      <c r="H50">
-        <v>0.01</v>
-      </c>
-      <c r="I50">
-        <v>0.1</v>
-      </c>
-      <c r="J50" t="s">
-        <v>40</v>
-      </c>
-      <c r="K50" t="s">
-        <v>41</v>
-      </c>
-      <c r="L50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" t="s">
-        <v>28</v>
-      </c>
-      <c r="C51" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" t="s">
-        <v>47</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
-        <v>81</v>
-      </c>
-      <c r="G51">
-        <v>0.9</v>
-      </c>
-      <c r="H51">
-        <v>0.75</v>
-      </c>
-      <c r="I51">
-        <v>0.99</v>
-      </c>
-      <c r="J51" t="s">
-        <v>40</v>
-      </c>
-      <c r="K51" t="s">
-        <v>41</v>
-      </c>
-      <c r="L51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" t="s">
-        <v>48</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>81</v>
-      </c>
-      <c r="G52">
-        <v>0.1</v>
-      </c>
-      <c r="H52">
-        <v>0.05</v>
-      </c>
-      <c r="I52">
-        <v>0.25</v>
-      </c>
-      <c r="J52" t="s">
-        <v>40</v>
-      </c>
-      <c r="K52" t="s">
-        <v>41</v>
-      </c>
-      <c r="L52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" t="s">
-        <v>72</v>
-      </c>
-      <c r="J53" t="s">
-        <v>40</v>
-      </c>
-      <c r="K53" t="s">
-        <v>41</v>
-      </c>
-      <c r="L53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>30</v>
-      </c>
-      <c r="B54" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" t="s">
-        <v>48</v>
-      </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" t="s">
-        <v>72</v>
-      </c>
-      <c r="J54" t="s">
-        <v>40</v>
-      </c>
-      <c r="K54" t="s">
-        <v>41</v>
-      </c>
-      <c r="L54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D55" t="s">
-        <v>48</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>74</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
-      <c r="I55">
-        <v>1</v>
-      </c>
-      <c r="J55" t="s">
-        <v>40</v>
-      </c>
-      <c r="K55" t="s">
-        <v>41</v>
-      </c>
-      <c r="L55" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" t="s">
-        <v>74</v>
-      </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="J56" t="s">
-        <v>40</v>
-      </c>
-      <c r="K56" t="s">
-        <v>41</v>
-      </c>
-      <c r="L56" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" t="s">
-        <v>44</v>
-      </c>
-      <c r="E57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" t="s">
-        <v>78</v>
-      </c>
-      <c r="G57">
-        <v>0.85</v>
-      </c>
-      <c r="H57">
-        <v>0.7</v>
-      </c>
-      <c r="I57">
-        <v>0.97</v>
-      </c>
-      <c r="J57" t="s">
-        <v>40</v>
-      </c>
-      <c r="K57" t="s">
-        <v>41</v>
-      </c>
-      <c r="L57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>30</v>
-      </c>
-      <c r="B58" t="s">
-        <v>28</v>
-      </c>
-      <c r="C58" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>78</v>
-      </c>
-      <c r="G58">
-        <v>0.15</v>
-      </c>
-      <c r="H58">
-        <v>0.05</v>
-      </c>
-      <c r="I58">
-        <v>0.2</v>
-      </c>
-      <c r="J58" t="s">
-        <v>40</v>
-      </c>
-      <c r="K58" t="s">
-        <v>41</v>
-      </c>
-      <c r="L58" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>30</v>
-      </c>
-      <c r="B59" t="s">
-        <v>28</v>
-      </c>
-      <c r="C59" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" t="s">
-        <v>48</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="s">
-        <v>74</v>
-      </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59">
-        <v>1</v>
-      </c>
-      <c r="J59" t="s">
-        <v>40</v>
-      </c>
-      <c r="K59" t="s">
-        <v>41</v>
-      </c>
-      <c r="L59" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>30</v>
-      </c>
-      <c r="B60" t="s">
-        <v>28</v>
-      </c>
-      <c r="C60" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" t="s">
-        <v>74</v>
-      </c>
-      <c r="G60">
-        <v>1</v>
-      </c>
-      <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60">
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>40</v>
-      </c>
-      <c r="K60" t="s">
-        <v>41</v>
-      </c>
-      <c r="L60" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>30</v>
-      </c>
-      <c r="B61" t="s">
-        <v>28</v>
-      </c>
-      <c r="C61" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>74</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>1</v>
-      </c>
-      <c r="I61">
-        <v>1</v>
-      </c>
-      <c r="J61" t="s">
-        <v>40</v>
-      </c>
-      <c r="K61" t="s">
-        <v>41</v>
-      </c>
-      <c r="L61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>30</v>
-      </c>
-      <c r="B62" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" t="s">
-        <v>70</v>
-      </c>
-      <c r="D62" t="s">
-        <v>39</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" t="s">
-        <v>77</v>
-      </c>
-      <c r="G62">
-        <v>0.85</v>
-      </c>
-      <c r="H62">
-        <v>0.66</v>
-      </c>
-      <c r="I62">
-        <v>0.94</v>
-      </c>
-      <c r="J62" t="s">
-        <v>40</v>
-      </c>
-      <c r="K62" t="s">
-        <v>41</v>
-      </c>
-      <c r="L62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>30</v>
-      </c>
-      <c r="B63" t="s">
-        <v>28</v>
-      </c>
-      <c r="C63" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" t="s">
-        <v>77</v>
-      </c>
-      <c r="G63">
-        <v>0.15</v>
-      </c>
-      <c r="H63">
-        <v>0.05</v>
-      </c>
-      <c r="I63">
-        <v>0.4</v>
-      </c>
-      <c r="J63" t="s">
-        <v>40</v>
-      </c>
-      <c r="K63" t="s">
-        <v>41</v>
-      </c>
-      <c r="L63" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>30</v>
-      </c>
-      <c r="B64" t="s">
-        <v>28</v>
-      </c>
-      <c r="C64" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>74</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64">
-        <v>1</v>
-      </c>
-      <c r="I64">
-        <v>1</v>
-      </c>
-      <c r="J64" t="s">
-        <v>40</v>
-      </c>
-      <c r="K64" t="s">
-        <v>41</v>
-      </c>
-      <c r="L64" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>30</v>
-      </c>
-      <c r="B65" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" t="s">
-        <v>71</v>
-      </c>
-      <c r="D65" t="s">
-        <v>42</v>
-      </c>
-      <c r="E65" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" t="s">
-        <v>76</v>
-      </c>
-      <c r="G65">
-        <v>0.72</v>
-      </c>
-      <c r="H65">
-        <v>0.34</v>
-      </c>
-      <c r="I65">
-        <v>0.94</v>
-      </c>
-      <c r="J65" t="s">
-        <v>40</v>
-      </c>
-      <c r="K65" t="s">
-        <v>41</v>
-      </c>
-      <c r="L65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>30</v>
-      </c>
-      <c r="B66" t="s">
-        <v>28</v>
-      </c>
-      <c r="C66" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="s">
-        <v>76</v>
-      </c>
-      <c r="G66">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H66">
-        <v>0.1</v>
-      </c>
-      <c r="I66">
-        <v>0.5</v>
-      </c>
-      <c r="J66" t="s">
-        <v>40</v>
-      </c>
-      <c r="K66" t="s">
-        <v>41</v>
-      </c>
-      <c r="L66" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>30</v>
-      </c>
-      <c r="B67" t="s">
-        <v>28</v>
-      </c>
-      <c r="C67" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" t="s">
-        <v>48</v>
-      </c>
-      <c r="E67" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" t="s">
-        <v>74</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <v>1</v>
-      </c>
-      <c r="I67">
-        <v>1</v>
-      </c>
-      <c r="J67" t="s">
-        <v>40</v>
-      </c>
-      <c r="K67" t="s">
-        <v>41</v>
-      </c>
-      <c r="L67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" t="s">
-        <v>49</v>
-      </c>
-      <c r="E68" t="s">
-        <v>28</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-      <c r="G68">
-        <v>0.02</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0.05</v>
-      </c>
-      <c r="J68" t="s">
-        <v>26</v>
-      </c>
-      <c r="K68" t="s">
-        <v>27</v>
-      </c>
-      <c r="L68" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" t="s">
-        <v>28</v>
-      </c>
-      <c r="F69" t="s">
-        <v>61</v>
-      </c>
-      <c r="G69">
-        <v>0.02</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0.05</v>
-      </c>
-      <c r="J69" t="s">
-        <v>26</v>
-      </c>
-      <c r="K69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L69" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" t="s">
-        <v>49</v>
-      </c>
-      <c r="E70" t="s">
-        <v>28</v>
-      </c>
-      <c r="F70" t="s">
-        <v>62</v>
-      </c>
-      <c r="G70">
-        <v>0.02</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0.05</v>
-      </c>
-      <c r="J70" t="s">
-        <v>26</v>
-      </c>
-      <c r="K70" t="s">
-        <v>27</v>
-      </c>
-      <c r="L70" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" t="s">
-        <v>28</v>
-      </c>
-      <c r="F71" t="s">
-        <v>63</v>
-      </c>
-      <c r="G71">
-        <v>0.02</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0.05</v>
-      </c>
-      <c r="J71" t="s">
-        <v>26</v>
-      </c>
-      <c r="K71" t="s">
-        <v>27</v>
-      </c>
-      <c r="L71" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" t="s">
-        <v>28</v>
-      </c>
-      <c r="F72" t="s">
-        <v>64</v>
-      </c>
-      <c r="G72">
-        <v>0.02</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0.05</v>
-      </c>
-      <c r="J72" t="s">
-        <v>26</v>
-      </c>
-      <c r="K72" t="s">
-        <v>27</v>
-      </c>
-      <c r="L72" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" t="s">
-        <v>49</v>
-      </c>
-      <c r="E73" t="s">
-        <v>28</v>
-      </c>
-      <c r="F73" t="s">
-        <v>65</v>
-      </c>
-      <c r="G73">
-        <v>0.02</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0.05</v>
-      </c>
-      <c r="J73" t="s">
-        <v>26</v>
-      </c>
-      <c r="K73" t="s">
-        <v>27</v>
-      </c>
-      <c r="L73" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" t="s">
-        <v>49</v>
-      </c>
-      <c r="E74" t="s">
-        <v>28</v>
-      </c>
-      <c r="F74" t="s">
-        <v>66</v>
-      </c>
-      <c r="G74">
-        <v>0.02</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0.05</v>
-      </c>
-      <c r="J74" t="s">
-        <v>26</v>
-      </c>
-      <c r="K74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L74" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>9</v>
-      </c>
-      <c r="B75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" t="s">
-        <v>49</v>
-      </c>
-      <c r="E75" t="s">
-        <v>28</v>
-      </c>
-      <c r="F75" t="s">
-        <v>67</v>
-      </c>
-      <c r="G75">
-        <v>0.02</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0.05</v>
-      </c>
-      <c r="J75" t="s">
-        <v>26</v>
-      </c>
-      <c r="K75" t="s">
-        <v>27</v>
-      </c>
-      <c r="L75" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" t="s">
-        <v>49</v>
-      </c>
-      <c r="E76" t="s">
-        <v>28</v>
-      </c>
-      <c r="F76" t="s">
-        <v>68</v>
-      </c>
-      <c r="G76">
-        <v>0.02</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0.05</v>
-      </c>
-      <c r="J76" t="s">
-        <v>26</v>
-      </c>
-      <c r="K76" t="s">
-        <v>27</v>
-      </c>
-      <c r="L76" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" t="s">
-        <v>49</v>
-      </c>
-      <c r="E77" t="s">
-        <v>28</v>
-      </c>
-      <c r="F77" t="s">
-        <v>69</v>
-      </c>
-      <c r="G77">
-        <v>0.02</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0.05</v>
-      </c>
-      <c r="J77" t="s">
-        <v>26</v>
-      </c>
-      <c r="K77" t="s">
-        <v>27</v>
-      </c>
-      <c r="L77" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" t="s">
-        <v>49</v>
-      </c>
-      <c r="E78" t="s">
-        <v>28</v>
-      </c>
-      <c r="F78" t="s">
-        <v>70</v>
-      </c>
-      <c r="G78">
-        <v>0.02</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>0.05</v>
-      </c>
-      <c r="J78" t="s">
-        <v>26</v>
-      </c>
-      <c r="K78" t="s">
-        <v>27</v>
-      </c>
-      <c r="L78" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" t="s">
-        <v>49</v>
-      </c>
-      <c r="E79" t="s">
-        <v>28</v>
-      </c>
-      <c r="F79" t="s">
-        <v>71</v>
-      </c>
-      <c r="G79">
-        <v>0.02</v>
-      </c>
-      <c r="H79">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>0.05</v>
-      </c>
-      <c r="J79" t="s">
-        <v>26</v>
-      </c>
-      <c r="K79" t="s">
-        <v>27</v>
-      </c>
-      <c r="L79" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" t="s">
-        <v>28</v>
-      </c>
-      <c r="C80" t="s">
-        <v>66</v>
-      </c>
-      <c r="D80" t="s">
-        <v>50</v>
-      </c>
-      <c r="E80" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" t="s">
-        <v>84</v>
-      </c>
-      <c r="J80" t="s">
-        <v>40</v>
-      </c>
-      <c r="K80" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" t="s">
-        <v>28</v>
-      </c>
-      <c r="C81" t="s">
-        <v>66</v>
-      </c>
-      <c r="D81" t="s">
-        <v>48</v>
-      </c>
-      <c r="E81" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" t="s">
-        <v>84</v>
-      </c>
-      <c r="J81" t="s">
-        <v>40</v>
-      </c>
-      <c r="K81" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" t="s">
-        <v>28</v>
-      </c>
-      <c r="C82" t="s">
-        <v>70</v>
-      </c>
-      <c r="D82" t="s">
-        <v>42</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>76</v>
-      </c>
-      <c r="J82" t="s">
-        <v>40</v>
-      </c>
-      <c r="K82" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>30</v>
-      </c>
-      <c r="B83" t="s">
-        <v>28</v>
-      </c>
-      <c r="C83" t="s">
-        <v>70</v>
-      </c>
-      <c r="D83" t="s">
-        <v>48</v>
-      </c>
-      <c r="E83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" t="s">
-        <v>76</v>
-      </c>
-      <c r="J83" t="s">
-        <v>40</v>
-      </c>
-      <c r="K83" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>30</v>
-      </c>
-      <c r="B84" t="s">
-        <v>28</v>
-      </c>
-      <c r="C84" t="s">
-        <v>65</v>
-      </c>
-      <c r="D84" t="s">
-        <v>51</v>
-      </c>
-      <c r="E84" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" t="s">
-        <v>85</v>
-      </c>
-      <c r="J84" t="s">
-        <v>40</v>
-      </c>
-      <c r="K84" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" t="s">
-        <v>28</v>
-      </c>
-      <c r="C85" t="s">
-        <v>65</v>
-      </c>
-      <c r="D85" t="s">
-        <v>48</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>85</v>
-      </c>
-      <c r="J85" t="s">
-        <v>40</v>
-      </c>
-      <c r="K85" t="s">
-        <v>41</v>
+      <c r="L85" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
